--- a/BURL.xlsx
+++ b/BURL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1980BE80-244E-4E7E-BE5D-44D7E5825596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD285976-44F2-45F8-B09B-B6DDD08457CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{C745F4EA-6A7E-4A07-A8BF-2B36F0EE508D}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{C745F4EA-6A7E-4A07-A8BF-2B36F0EE508D}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -253,16 +253,14 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -301,35 +299,38 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -683,7 +684,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="2">
-        <v>358.03</v>
+        <v>294.94</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -691,10 +692,10 @@
         <v>3</v>
       </c>
       <c r="I3" s="6">
-        <v>62.942205999999999</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>54</v>
+        <v>63.896000000000001</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -706,21 +707,21 @@
       </c>
       <c r="I4" s="3">
         <f>+I2*I3</f>
-        <v>22535.198014179998</v>
+        <v>18845.486239999998</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="I5" s="3">
-        <v>747.35500000000002</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>54</v>
+        <v>703.68600000000004</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -728,11 +729,10 @@
         <v>6</v>
       </c>
       <c r="I6" s="3">
-        <f>20.02+1897.343</f>
-        <v>1917.3630000000001</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>54</v>
+        <v>1893.511</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -741,7 +741,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>23705.206014179999</v>
+        <v>20035.311239999995</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -754,6 +754,9 @@
       <c r="J10" s="3"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{3053613E-0124-492A-B2B5-4114B1194DC2}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -926,7 +929,9 @@
       <c r="O5" s="6">
         <v>2852.31</v>
       </c>
-      <c r="P5" s="6"/>
+      <c r="P5" s="6">
+        <v>2997.7779999999998</v>
+      </c>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
       <c r="S5" s="6"/>
@@ -1011,7 +1016,9 @@
       <c r="O6" s="6">
         <v>4.1509999999999998</v>
       </c>
-      <c r="P6" s="6"/>
+      <c r="P6" s="6">
+        <v>4.4850000000000003</v>
+      </c>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
       <c r="S6" s="6"/>
@@ -1121,7 +1128,9 @@
         <f t="shared" si="1"/>
         <v>2856.4609999999998</v>
       </c>
-      <c r="P7" s="7"/>
+      <c r="P7" s="7">
+        <v>3002.2629999999999</v>
+      </c>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
       <c r="S7" s="6"/>
@@ -1209,7 +1218,9 @@
       <c r="O8" s="6">
         <v>1594.8040000000001</v>
       </c>
-      <c r="P8" s="6"/>
+      <c r="P8" s="6">
+        <v>1614.011</v>
+      </c>
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
       <c r="S8" s="6"/>
@@ -1296,7 +1307,7 @@
         <v>1112.5529999999999</v>
       </c>
       <c r="J9" s="6">
-        <f t="shared" ref="J9:O9" si="4">+J7-J8</f>
+        <f t="shared" ref="J9:P9" si="4">+J7-J8</f>
         <v>0</v>
       </c>
       <c r="K9" s="6">
@@ -1319,7 +1330,10 @@
         <f t="shared" si="4"/>
         <v>1261.6569999999997</v>
       </c>
-      <c r="P9" s="6"/>
+      <c r="P9" s="6">
+        <f t="shared" si="4"/>
+        <v>1388.252</v>
+      </c>
       <c r="Q9" s="6"/>
       <c r="R9" s="6"/>
       <c r="S9" s="6"/>
@@ -1422,7 +1436,9 @@
       <c r="O10" s="6">
         <v>989.37400000000002</v>
       </c>
-      <c r="P10" s="6"/>
+      <c r="P10" s="6">
+        <v>1019.173</v>
+      </c>
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
@@ -1507,7 +1523,9 @@
       <c r="O11" s="6">
         <v>15.315</v>
       </c>
-      <c r="P11" s="6"/>
+      <c r="P11" s="6">
+        <v>0</v>
+      </c>
       <c r="Q11" s="6"/>
       <c r="R11" s="6"/>
       <c r="S11" s="6"/>
@@ -1592,7 +1610,9 @@
       <c r="O12" s="6">
         <v>104.607</v>
       </c>
-      <c r="P12" s="6"/>
+      <c r="P12" s="6">
+        <v>114.02200000000001</v>
+      </c>
       <c r="Q12" s="6"/>
       <c r="R12" s="6"/>
       <c r="S12" s="6"/>
@@ -1677,7 +1697,9 @@
       <c r="O13" s="6">
         <v>0.80700000000000005</v>
       </c>
-      <c r="P13" s="6"/>
+      <c r="P13" s="6">
+        <v>3.577</v>
+      </c>
       <c r="Q13" s="6"/>
       <c r="R13" s="6"/>
       <c r="S13" s="6"/>
@@ -1762,7 +1784,9 @@
       <c r="O14" s="6">
         <v>1.4490000000000001</v>
       </c>
-      <c r="P14" s="6"/>
+      <c r="P14" s="6">
+        <v>4.1559999999999997</v>
+      </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
@@ -1849,7 +1873,7 @@
         <v>137.23899999999986</v>
       </c>
       <c r="J15" s="6">
-        <f t="shared" ref="J15:O15" si="7">+J9-SUM(J10:J13)+J14</f>
+        <f t="shared" ref="J15:P15" si="7">+J9-SUM(J10:J13)+J14</f>
         <v>0</v>
       </c>
       <c r="K15" s="6">
@@ -1872,7 +1896,10 @@
         <f t="shared" si="7"/>
         <v>153.00299999999964</v>
       </c>
-      <c r="P15" s="6"/>
+      <c r="P15" s="6">
+        <f t="shared" si="7"/>
+        <v>255.63600000000002</v>
+      </c>
       <c r="Q15" s="6"/>
       <c r="R15" s="6"/>
       <c r="S15" s="6"/>
@@ -1975,7 +2002,9 @@
       <c r="O16" s="6">
         <v>0</v>
       </c>
-      <c r="P16" s="6"/>
+      <c r="P16" s="6">
+        <v>0</v>
+      </c>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
       <c r="S16" s="6"/>
@@ -2062,7 +2091,10 @@
         <f>16.495-6.161</f>
         <v>10.334000000000001</v>
       </c>
-      <c r="P17" s="6"/>
+      <c r="P17" s="6">
+        <f>19.659-6.14</f>
+        <v>13.518999999999998</v>
+      </c>
       <c r="Q17" s="6"/>
       <c r="R17" s="6"/>
       <c r="S17" s="6"/>
@@ -2152,7 +2184,7 @@
         <v>118.05799999999985</v>
       </c>
       <c r="J18" s="6">
-        <f t="shared" ref="J18:O18" si="10">+J15-J16-J17</f>
+        <f t="shared" ref="J18:P18" si="10">+J15-J16-J17</f>
         <v>0</v>
       </c>
       <c r="K18" s="6">
@@ -2175,7 +2207,10 @@
         <f t="shared" si="10"/>
         <v>142.66899999999964</v>
       </c>
-      <c r="P18" s="6"/>
+      <c r="P18" s="6">
+        <f t="shared" si="10"/>
+        <v>242.11700000000002</v>
+      </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
       <c r="S18" s="6"/>
@@ -2278,7 +2313,9 @@
       <c r="O19" s="6">
         <v>27.925000000000001</v>
       </c>
-      <c r="P19" s="6"/>
+      <c r="P19" s="6">
+        <v>57.813000000000002</v>
+      </c>
       <c r="Q19" s="6"/>
       <c r="R19" s="6"/>
       <c r="S19" s="6"/>
@@ -2365,7 +2402,7 @@
         <v>90.616999999999848</v>
       </c>
       <c r="J20" s="6">
-        <f t="shared" ref="J20:O20" si="13">+J18-J19</f>
+        <f t="shared" ref="J20:P20" si="13">+J18-J19</f>
         <v>0</v>
       </c>
       <c r="K20" s="6">
@@ -2388,7 +2425,10 @@
         <f t="shared" si="13"/>
         <v>114.74399999999964</v>
       </c>
-      <c r="P20" s="6"/>
+      <c r="P20" s="6">
+        <f t="shared" si="13"/>
+        <v>184.30400000000003</v>
+      </c>
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
       <c r="S20" s="6"/>
@@ -2555,7 +2595,7 @@
         <v>1.4256249705017046</v>
       </c>
       <c r="J22" s="6" t="e">
-        <f t="shared" ref="J22:O22" si="16">+J20/J23</f>
+        <f t="shared" ref="J22:P22" si="16">+J20/J23</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K22" s="6">
@@ -2578,7 +2618,10 @@
         <f t="shared" si="16"/>
         <v>1.8282982791586941</v>
       </c>
-      <c r="P22" s="6"/>
+      <c r="P22" s="6">
+        <f t="shared" si="16"/>
+        <v>2.8844372104670093</v>
+      </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
@@ -2666,7 +2709,9 @@
       <c r="O23" s="6">
         <v>62.76</v>
       </c>
-      <c r="P23" s="6"/>
+      <c r="P23" s="6">
+        <v>63.896000000000001</v>
+      </c>
       <c r="Q23" s="6"/>
       <c r="R23" s="6"/>
       <c r="S23" s="6"/>
